--- a/output/full_scan/batch_seq6_2026-07-03.xlsx
+++ b/output/full_scan/batch_seq6_2026-07-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6175</v>
+        <v>6226</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>744.2004340239911</v>
+        <v>755.1426352828923</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.41932036452871</v>
+        <v>75.15852982344182</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>38.67073437003843</v>
+        <v>37.58375389022251</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6143998357405368</v>
+        <v>1.114263528289239</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.8504399327584151</v>
+        <v>1.291802272235745</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6284</v>
+        <v>6175</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>740.9997592317034</v>
+        <v>744.2004340239911</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.00655510644673</v>
+        <v>60.41932036452871</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.17154987220425</v>
+        <v>38.67073437003843</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.160899221807001</v>
+        <v>0.6143998357405368</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0596207836856845</v>
+        <v>-0.8504399327584151</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6213</v>
+        <v>6284</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>740.6990826773147</v>
+        <v>740.9997592317034</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>394</v>
+        <v>108</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>73.39791631141713</v>
+        <v>57.00655510644673</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.09023117746602</v>
+        <v>34.17154987220425</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.656725533027008</v>
+        <v>1.160899221807001</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>9.733118591334254</v>
+        <v>0.0596207836856845</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6418</v>
+        <v>6213</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>731.5545168333206</v>
+        <v>740.6990826773147</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.45</v>
+        <v>394</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.73100761330584</v>
+        <v>73.39791631141713</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.9962404910572</v>
+        <v>24.09023117746602</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.341096999493268</v>
+        <v>1.656725533027008</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2129409995278076</v>
+        <v>9.733118591334254</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6197</v>
+        <v>6418</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>723.1875898052259</v>
+        <v>731.5545168333206</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>372.5</v>
+        <v>34.45</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>67.73312983788406</v>
+        <v>63.73100761330584</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.12705624091632</v>
+        <v>20.9962404910572</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6212476798413424</v>
+        <v>1.341096999493268</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.987276042599028</v>
+        <v>0.2129409995278076</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6271</v>
+        <v>6197</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>713.5160578673618</v>
+        <v>723.1875898052259</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>279</v>
+        <v>372.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.12857828352572</v>
+        <v>67.73312983788406</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.37334400550106</v>
+        <v>41.12705624091632</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.882148185385197</v>
+        <v>0.6212476798413424</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.7110736589861</v>
+        <v>-1.987276042599028</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6274</v>
+        <v>6271</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>686.4358207101609</v>
+        <v>713.5160578673618</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1790</v>
+        <v>279</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.73726282029462</v>
+        <v>59.12857828352572</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25.17380831515328</v>
+        <v>27.37334400550106</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.215849660852762</v>
+        <v>1.882148185385197</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-9.770506417903109</v>
+        <v>1.7110736589861</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6207</v>
+        <v>6243</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>676.3968506736325</v>
+        <v>706.5527925507809</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>154</v>
+        <v>40.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.485240270818</v>
+        <v>58.61327511505427</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>54.24951513318878</v>
+        <v>31.70538706226754</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5217051789658541</v>
+        <v>0.1695101086840616</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.299155124278059</v>
+        <v>0.3129588423461675</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6477</v>
+        <v>6274</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>658.0339582810473</v>
+        <v>686.4358207101609</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>36.9</v>
+        <v>1790</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.80443213135344</v>
+        <v>59.73726282029462</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.1153968685869</v>
+        <v>25.17380831515328</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.403395828104725</v>
+        <v>1.215849660852762</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.482791609823466</v>
+        <v>-9.770506417903109</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6257</v>
+        <v>6207</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>655.6593312845155</v>
+        <v>676.3968506736325</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>254.5</v>
+        <v>154</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.81978159155065</v>
+        <v>58.485240270818</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.58141370855805</v>
+        <v>54.24951513318878</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7786306277908397</v>
+        <v>0.5217051789658541</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.908973481292832</v>
+        <v>-2.299155124278059</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6164</v>
+        <v>6477</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>651.4558933961798</v>
+        <v>658.0339582810473</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>17.4</v>
+        <v>36.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>77.63386172971151</v>
+        <v>63.80443213135344</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>29.53432433113055</v>
+        <v>15.1153968685869</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.745589339617986</v>
+        <v>4.403395828104725</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3574641176307063</v>
+        <v>0.482791609823466</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6432</v>
+        <v>6257</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>650.4428085425216</v>
+        <v>655.6593312845155</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>254.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.7435574656837</v>
+        <v>64.81978159155065</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>34.94239746600598</v>
+        <v>24.58141370855805</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7389311158248393</v>
+        <v>0.7786306277908397</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.8529952824787879</v>
+        <v>1.908973481292832</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6472</v>
+        <v>6164</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>649.8791248025724</v>
+        <v>651.4558933961798</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>439.5</v>
+        <v>17.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.66170134925127</v>
+        <v>77.63386172971151</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28.15329009977769</v>
+        <v>29.53432433113055</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.47026028738724</v>
+        <v>2.745589339617986</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.091624828460635</v>
+        <v>0.3574641176307063</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6259</v>
+        <v>6432</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>623.8265717806735</v>
+        <v>650.4428085425216</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>40.05</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>63.36471030681354</v>
+        <v>57.7435574656837</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>40.91887498404749</v>
+        <v>34.94239746600598</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.451031934867456</v>
+        <v>0.7389311158248393</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2475184438475386</v>
+        <v>-0.8529952824787879</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6209</v>
+        <v>6472</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>603.0137950346095</v>
+        <v>649.8791248025724</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>80</v>
+        <v>439.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46.15094916418382</v>
+        <v>60.66170134925127</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.45613788071748</v>
+        <v>28.15329009977769</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.1326304462178276</v>
+        <v>1.47026028738724</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.899946002111652</v>
+        <v>2.091624828460635</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6270</v>
+        <v>6259</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>602.2280035454544</v>
+        <v>623.8265717806735</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>36.6</v>
+        <v>40.05</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.49483855615532</v>
+        <v>63.36471030681354</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>49.01677734286089</v>
+        <v>40.91887498404749</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1798287957424</v>
+        <v>1.451031934867456</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.3938571303043905</v>
+        <v>0.2475184438475386</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6419</v>
+        <v>6209</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>599.2393469487348</v>
+        <v>603.0137950346095</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.15607417568884</v>
+        <v>46.15094916418382</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.72663536966219</v>
+        <v>31.45613788071748</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.453539587511191</v>
+        <v>0.1326304462178276</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0509978955558522</v>
+        <v>-1.899946002111652</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6168</v>
+        <v>6270</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>596.4686248858485</v>
+        <v>602.2280035454544</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.9</v>
+        <v>36.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.72381300102199</v>
+        <v>53.49483855615532</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.3177650681849</v>
+        <v>49.01677734286089</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2440481528041063</v>
+        <v>0.1798287957424</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0484069526407324</v>
+        <v>-0.3938571303043905</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6204</v>
+        <v>6419</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>591.0842594824036</v>
+        <v>599.2393469487348</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.67045264214952</v>
+        <v>52.15607417568884</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34.42312149661753</v>
+        <v>10.72663536966219</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.769553342382793</v>
+        <v>0.453539587511191</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.2716585603697332</v>
+        <v>0.0509978955558522</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6411</v>
+        <v>6168</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>590.4391033524898</v>
+        <v>596.4686248858485</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>99.7</v>
+        <v>29.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.8805775678884</v>
+        <v>52.72381300102199</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.11067478253257</v>
+        <v>26.3177650681849</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.446431432044802</v>
+        <v>0.2440481528041063</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.738798011680506</v>
+        <v>-0.0484069526407324</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6208</v>
+        <v>6204</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>589.6965362573865</v>
+        <v>591.0842594824036</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>96.8</v>
+        <v>122</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.49804022387153</v>
+        <v>60.67045264214952</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.32435195917092</v>
+        <v>34.42312149661753</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5646298745779726</v>
+        <v>0.769553342382793</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.4703916910029742</v>
+        <v>-0.2716585603697332</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6196</v>
+        <v>6411</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>586.087038508518</v>
+        <v>590.4391033524898</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>588</v>
+        <v>99.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>66.24332136713667</v>
+        <v>51.8805775678884</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33.76647659164092</v>
+        <v>26.11067478253257</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7302240586630384</v>
+        <v>0.446431432044802</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.2180153155053048</v>
+        <v>-0.738798011680506</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6446</v>
+        <v>6208</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>582.3928003474779</v>
+        <v>589.6965362573865</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1395</v>
+        <v>96.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>84.65542265071268</v>
+        <v>53.49804022387153</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>54.37161105910083</v>
+        <v>17.32435195917092</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.034948690439859</v>
+        <v>0.5646298745779726</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>27.59533689381092</v>
+        <v>-0.4703916910029742</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6202</v>
+        <v>6196</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>575.3710426087378</v>
+        <v>586.087038508518</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>67</v>
+        <v>588</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.60632274401835</v>
+        <v>66.24332136713667</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.6278422649872</v>
+        <v>33.76647659164092</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9312814473734496</v>
+        <v>0.7302240586630384</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0466507721940852</v>
+        <v>-0.2180153155053048</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6451</v>
+        <v>6446</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>569.0345485201806</v>
+        <v>582.3928003474779</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>543</v>
+        <v>1395</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.3885871528324</v>
+        <v>84.65542265071268</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.67868421956487</v>
+        <v>54.37161105910083</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6592466204241365</v>
+        <v>1.034948690439859</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-9.824502876096499</v>
+        <v>27.59533689381092</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6266</v>
+        <v>6415</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>564.0731715551332</v>
+        <v>578.0944197602432</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.85</v>
+        <v>605</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.1416108456954</v>
+        <v>54.59502776804068</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.6970219728148</v>
+        <v>21.37798215079343</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7882515978363196</v>
+        <v>0.2752963738064421</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0276459964253371</v>
+        <v>-2.746006558726385</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6220</v>
+        <v>6202</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>558.4394112148094</v>
+        <v>575.3710426087378</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>34.4</v>
+        <v>67</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.22393372906131</v>
+        <v>55.60632274401835</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>44.05657620478269</v>
+        <v>29.6278422649872</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4758841835140553</v>
+        <v>0.9312814473734496</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.5736230063337677</v>
+        <v>-0.0466507721940852</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6409</v>
+        <v>6451</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>541.4776690127349</v>
+        <v>569.0345485201806</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1255</v>
+        <v>543</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>80.99657895954226</v>
+        <v>47.3885871528324</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>49.43823607426321</v>
+        <v>26.67868421956487</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.247766901273482</v>
+        <v>0.6592466204241365</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>28.0968981306487</v>
+        <v>-9.824502876096499</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6239</v>
+        <v>6266</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>540.8125037033323</v>
+        <v>564.0731715551332</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>338</v>
+        <v>25.85</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.58188565309455</v>
+        <v>47.1416108456954</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>26.61852113296501</v>
+        <v>23.6970219728148</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5198775357926223</v>
+        <v>0.7882515978363196</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-4.03691414513383</v>
+        <v>0.0276459964253371</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6261</v>
+        <v>6220</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>539.4296745048676</v>
+        <v>558.4394112148094</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>34.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.11844805085574</v>
+        <v>48.22393372906131</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.92028155903133</v>
+        <v>44.05657620478269</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4080560181655605</v>
+        <v>0.4758841835140553</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0417289562554277</v>
+        <v>-0.5736230063337677</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6191</v>
+        <v>6409</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>538.7474141414243</v>
+        <v>541.4776690127349</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>108</v>
+        <v>1255</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>60.11783952260471</v>
+        <v>80.99657895954226</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.02930927827657</v>
+        <v>49.43823607426321</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.174741414142424</v>
+        <v>1.247766901273482</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.999427045708054</v>
+        <v>28.0968981306487</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6275</v>
+        <v>6239</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>535.3777444837945</v>
+        <v>540.8125037033323</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>50.2</v>
+        <v>338</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.99810819603903</v>
+        <v>54.58188565309455</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.77534273801711</v>
+        <v>26.61852113296501</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5087208438044316</v>
+        <v>0.5198775357926223</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0948768180848584</v>
+        <v>-4.03691414513383</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6438</v>
+        <v>6261</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>528.4277504827863</v>
+        <v>539.4296745048676</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>165</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.64767171204758</v>
+        <v>46.11844805085574</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.38729206586047</v>
+        <v>19.92028155903133</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8929787859392717</v>
+        <v>0.4080560181655605</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.402186518558469</v>
+        <v>0.0417289562554277</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6417</v>
+        <v>6191</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>528.0428767151491</v>
+        <v>538.7474141414243</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.07789917492613</v>
+        <v>60.11783952260471</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10.99849743945493</v>
+        <v>27.02930927827657</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7914250534490869</v>
+        <v>1.174741414142424</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1522780057532408</v>
+        <v>0.999427045708054</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6449</v>
+        <v>6275</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>523.3141501713061</v>
+        <v>535.3777444837945</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>351</v>
+        <v>50.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.96517362036243</v>
+        <v>52.99810819603903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.09515470328152</v>
+        <v>13.77534273801711</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.23287783984965</v>
+        <v>0.5087208438044316</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-12.99785100306129</v>
+        <v>0.0948768180848584</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6435</v>
+        <v>6438</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>523.1828598002369</v>
+        <v>528.4277504827863</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>382</v>
+        <v>165</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>68.75257692505917</v>
+        <v>55.64767171204758</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>37.76470868577341</v>
+        <v>21.38729206586047</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3.307627887882153</v>
+        <v>0.8929787859392717</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>4.296550833060376</v>
+        <v>2.402186518558469</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6282</v>
+        <v>6417</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>522.2993943547657</v>
+        <v>528.0428767151491</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>58.3</v>
+        <v>134</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.24624719547665</v>
+        <v>53.07789917492613</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.48666794502277</v>
+        <v>10.99849743945493</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2917438296923854</v>
+        <v>0.7914250534490869</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.4463205799455646</v>
+        <v>-0.1522780057532408</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6185</v>
+        <v>6449</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>515.128635276344</v>
+        <v>523.3141501713061</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>14.65</v>
+        <v>351</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.35065562847596</v>
+        <v>48.96517362036243</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.65632042743714</v>
+        <v>24.09515470328152</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.112863527634395</v>
+        <v>1.23287783984965</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0214442764122393</v>
+        <v>-12.99785100306129</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6269</v>
+        <v>6435</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>512.829549085222</v>
+        <v>523.1828598002369</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>66.8</v>
+        <v>382</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.36288396942324</v>
+        <v>68.75257692505917</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.3022546976034</v>
+        <v>37.76470868577341</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2891372566692405</v>
+        <v>3.307627887882153</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.720116769864466</v>
+        <v>4.296550833060376</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6176</v>
+        <v>6282</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>504.2743852198026</v>
+        <v>522.2993943547657</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>90.3</v>
+        <v>58.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.9400807672878</v>
+        <v>50.24624719547665</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.75034174057784</v>
+        <v>25.48666794502277</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8310482300263361</v>
+        <v>0.2917438296923854</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2435875252193775</v>
+        <v>-0.4463205799455646</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6234</v>
+        <v>6185</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>499.4358867240123</v>
+        <v>515.128635276344</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>49.4</v>
+        <v>14.65</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.99028602822609</v>
+        <v>58.35065562847596</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.89782210452871</v>
+        <v>18.65632042743714</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.447789508463011</v>
+        <v>1.112863527634395</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3447528379077801</v>
+        <v>0.0214442764122393</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6263</v>
+        <v>6269</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>497.4219755916997</v>
+        <v>512.829549085222</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>168</v>
+        <v>66.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.18792010970863</v>
+        <v>45.36288396942324</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.53349366983468</v>
+        <v>23.3022546976034</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8618018597826741</v>
+        <v>0.2891372566692405</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.2130031950173161</v>
+        <v>-1.720116769864466</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6235</v>
+        <v>6176</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>491.1091132557662</v>
+        <v>504.2743852198026</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>44.2</v>
+        <v>90.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>59.93138426490141</v>
+        <v>44.9400807672878</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.58799034493369</v>
+        <v>21.75034174057784</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.87052784543954</v>
+        <v>0.8310482300263361</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3042391092788217</v>
+        <v>0.2435875252193775</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6279</v>
+        <v>6234</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>489.6280707407635</v>
+        <v>499.4358867240123</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>123.5</v>
+        <v>49.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>60.39551498275778</v>
+        <v>54.99028602822609</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.20796970255168</v>
+        <v>13.89782210452871</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.579152750893451</v>
+        <v>1.447789508463011</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.06462735798224831</v>
+        <v>0.3447528379077801</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6189</v>
+        <v>6263</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>487.2397926867516</v>
+        <v>497.4219755916997</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>53.3</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.36707894495635</v>
+        <v>53.18792010970863</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.9167948511279</v>
+        <v>11.53349366983468</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2476621864471051</v>
+        <v>0.8618018597826741</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.2729486002678786</v>
+        <v>-0.2130031950173161</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6190</v>
+        <v>6235</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>482.6931471603545</v>
+        <v>491.1091132557662</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>85.8</v>
+        <v>44.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>58.94063349959227</v>
+        <v>59.93138426490141</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.57806968470316</v>
+        <v>13.58799034493369</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8645841064695604</v>
+        <v>3.87052784543954</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.228547392667199</v>
+        <v>0.3042391092788217</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6246</v>
+        <v>6279</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>481.1420483510558</v>
+        <v>489.6280707407635</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>16.05</v>
+        <v>123.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.8861563586269</v>
+        <v>60.39551498275778</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.52129827203058</v>
+        <v>14.20796970255168</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4256768695590454</v>
+        <v>2.579152750893451</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0379484641135884</v>
+        <v>-0.06462735798224831</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6166</v>
+        <v>6189</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>466.9358383009265</v>
+        <v>487.2397926867516</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>134</v>
+        <v>53.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.17606537670623</v>
+        <v>53.36707894495635</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>47.60783310728889</v>
+        <v>20.9167948511279</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3177268490432767</v>
+        <v>0.2476621864471051</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-3.149284158829579</v>
+        <v>-0.2729486002678786</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6229</v>
+        <v>6190</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>465.5069051725012</v>
+        <v>482.6931471603545</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27.4</v>
+        <v>85.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.60883675135756</v>
+        <v>58.94063349959227</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10.65486615867773</v>
+        <v>18.57806968470316</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4745707488691317</v>
+        <v>0.8645841064695604</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0198380493619581</v>
+        <v>0.228547392667199</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6292</v>
+        <v>6246</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>463.281619190668</v>
+        <v>481.1420483510558</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>61.8</v>
+        <v>16.05</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.23947003595838</v>
+        <v>53.8861563586269</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.24283933267542</v>
+        <v>23.52129827203058</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5404843753817876</v>
+        <v>0.4256768695590454</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.4615100482532037</v>
+        <v>0.0379484641135884</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6412</v>
+        <v>6166</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>460.0671965479385</v>
+        <v>466.9358383009265</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>57.01722115241506</v>
+        <v>50.17606537670623</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.51966344239194</v>
+        <v>47.60783310728889</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.848022453368063</v>
+        <v>0.3177268490432767</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3566065538727122</v>
+        <v>-3.149284158829579</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6465</v>
+        <v>6229</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>459.7470290542286</v>
+        <v>465.5069051725012</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>62.4</v>
+        <v>27.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.70609943569355</v>
+        <v>53.60883675135756</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>31.77858405864048</v>
+        <v>10.65486615867773</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2687102698457716</v>
+        <v>0.4745707488691317</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.944102662600538</v>
+        <v>-0.0198380493619581</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6217</v>
+        <v>6292</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>459.4603346535252</v>
+        <v>463.281619190668</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>269</v>
+        <v>61.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.92005280589559</v>
+        <v>51.23947003595838</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.24063318192069</v>
+        <v>26.24283933267542</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8873307821237809</v>
+        <v>0.5404843753817876</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>2.0829058875992</v>
+        <v>-0.4615100482532037</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6265</v>
+        <v>6412</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>458.814239381702</v>
+        <v>460.0671965479385</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>51.9</v>
+        <v>98</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.76120249214566</v>
+        <v>57.01722115241506</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.98123772303969</v>
+        <v>15.51966344239194</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2087434587223918</v>
+        <v>0.848022453368063</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.124473646439494</v>
+        <v>0.3566065538727122</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6215</v>
+        <v>6465</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>439.0550370346474</v>
+        <v>459.7470290542286</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>112.5</v>
+        <v>62.4</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.76065177768135</v>
+        <v>54.70609943569355</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.27589228105481</v>
+        <v>31.77858405864048</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.129852474047937</v>
+        <v>0.2687102698457716</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.02732455212206</v>
+        <v>-0.944102662600538</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6462</v>
+        <v>6217</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>422.0254076155347</v>
+        <v>459.4603346535252</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>117.5</v>
+        <v>269</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.98669398873499</v>
+        <v>52.92005280589559</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.0019612324739</v>
+        <v>15.24063318192069</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4699686510737949</v>
+        <v>0.8873307821237809</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3208393622048779</v>
+        <v>2.0829058875992</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6290</v>
+        <v>6265</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>421.6581993592927</v>
+        <v>458.814239381702</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>316</v>
+        <v>51.9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.16734360231169</v>
+        <v>46.76120249214566</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.76614667910912</v>
+        <v>22.98123772303969</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6349706555342145</v>
+        <v>0.2087434587223918</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.9249503064616786</v>
+        <v>-1.124473646439494</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6414</v>
+        <v>6215</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>419.0259451188973</v>
+        <v>439.0550370346474</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>375.5</v>
+        <v>112.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.86706803374297</v>
+        <v>51.76065177768135</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.1125018926793</v>
+        <v>19.27589228105481</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3225506089007429</v>
+        <v>2.129852474047937</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.143950598603863</v>
+        <v>1.02732455212206</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6278</v>
+        <v>6462</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>416.59439060527</v>
+        <v>422.0254076155347</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>212</v>
+        <v>117.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.93425416114429</v>
+        <v>47.98669398873499</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.51973379688163</v>
+        <v>17.0019612324739</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7619798205002184</v>
+        <v>0.4699686510737949</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3158384232901188</v>
+        <v>0.3208393622048779</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6233</v>
+        <v>6290</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>416.2810738523357</v>
+        <v>421.6581993592927</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>25.75</v>
+        <v>316</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.89923849071863</v>
+        <v>54.16734360231169</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.13538972519331</v>
+        <v>10.76614667910912</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.015398843552169</v>
+        <v>0.6349706555342145</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1235571534243093</v>
+        <v>-0.9249503064616786</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6214</v>
+        <v>6414</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>414.6063396934852</v>
+        <v>419.0259451188973</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>133.5</v>
+        <v>375.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.6336246839254</v>
+        <v>53.86706803374297</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.64303248851357</v>
+        <v>16.1125018926793</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6681328756628309</v>
+        <v>0.3225506089007429</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.174369161677104</v>
+        <v>-2.143950598603863</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6244</v>
+        <v>6278</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>411.0612481096992</v>
+        <v>416.59439060527</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>27.2</v>
+        <v>212</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.14312350235707</v>
+        <v>53.93425416114429</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.47957533797324</v>
+        <v>19.51973379688163</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2353510070113901</v>
+        <v>0.7619798205002184</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2068768062424432</v>
+        <v>0.3158384232901188</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6423</v>
+        <v>6233</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>389.9488003979612</v>
+        <v>416.2810738523357</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>81.7</v>
+        <v>25.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.35822735021812</v>
+        <v>52.89923849071863</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.42153627655556</v>
+        <v>12.13538972519331</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9049418506434588</v>
+        <v>1.015398843552169</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.7165579607405679</v>
+        <v>0.1235571534243093</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6470</v>
+        <v>6214</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>388.415818596619</v>
+        <v>414.6063396934852</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>49.3</v>
+        <v>133.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.41339478841638</v>
+        <v>48.6336246839254</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.68527203322914</v>
+        <v>18.64303248851357</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4025249358413714</v>
+        <v>0.6681328756628309</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1302978289952605</v>
+        <v>-1.174369161677104</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6192</v>
+        <v>6244</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>382.8993389401766</v>
+        <v>411.0612481096992</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>120.5</v>
+        <v>27.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.7961692763086</v>
+        <v>45.14312350235707</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.42378494631601</v>
+        <v>12.47957533797324</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.252415140813068</v>
+        <v>0.2353510070113901</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1400309504541743</v>
+        <v>-0.2068768062424432</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6228</v>
+        <v>6423</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>376.321883881066</v>
+        <v>389.9488003979612</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>19.65</v>
+        <v>81.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.32910550355839</v>
+        <v>40.35822735021812</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4.292030818004301</v>
+        <v>27.42153627655556</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2086496496535169</v>
+        <v>0.9049418506434588</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0492267652866736</v>
+        <v>0.7165579607405679</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6464</v>
+        <v>6470</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>374.7602230880304</v>
+        <v>388.415818596619</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>76.7</v>
+        <v>49.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>33.15895429321414</v>
+        <v>52.41339478841638</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.70060535637094</v>
+        <v>11.68527203322914</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.12991101274121</v>
+        <v>0.4025249358413714</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1472233488893781</v>
+        <v>-0.1302978289952605</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6227</v>
+        <v>6192</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>364.461021830007</v>
+        <v>382.8993389401766</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>124.5</v>
+        <v>120.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.85432950317984</v>
+        <v>46.7961692763086</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.23648548048383</v>
+        <v>20.42378494631601</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3867651827498828</v>
+        <v>1.252415140813068</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.7747318487993169</v>
+        <v>0.1400309504541743</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6291</v>
+        <v>6228</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>351.952211214578</v>
+        <v>376.321883881066</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>534</v>
+        <v>19.65</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.42984050195098</v>
+        <v>46.32910550355839</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.40589750142888</v>
+        <v>4.292030818004301</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5828268975134632</v>
+        <v>0.2086496496535169</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-7.120950690913377</v>
+        <v>-0.0492267652866736</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6237</v>
+        <v>6464</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>349.5821208250125</v>
+        <v>374.7602230880304</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>45.25</v>
+        <v>76.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.37743538766485</v>
+        <v>33.15895429321414</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.03071417977997</v>
+        <v>24.70060535637094</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.123343141676682</v>
+        <v>0.12991101274121</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2986318058569598</v>
+        <v>-0.1472233488893781</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6187</v>
+        <v>6227</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>347.2191248846516</v>
+        <v>364.461021830007</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1030</v>
+        <v>124.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,49 +4739,49 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.59198236507806</v>
+        <v>53.85432950317984</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.49047660498223</v>
+        <v>14.23648548048383</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.024155957910955</v>
+        <v>0.3867651827498828</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-13.13245810298604</v>
+        <v>-0.7747318487993169</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6170</v>
+        <v>6291</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>342.4213604482667</v>
+        <v>351.952211214578</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>52.2</v>
+        <v>534</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.81533579901885</v>
+        <v>47.42984050195098</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.29377246000271</v>
+        <v>14.40589750142888</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9028279746001536</v>
+        <v>0.5828268975134632</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0540520062518024</v>
+        <v>-7.120950690913377</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6188</v>
+        <v>6237</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>332.6599658514053</v>
+        <v>349.5821208250125</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>80.3</v>
+        <v>45.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.40393741201001</v>
+        <v>47.37743538766485</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.00704969377108</v>
+        <v>16.03071417977997</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.076589161423931</v>
+        <v>1.123343141676682</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.3392305759736631</v>
+        <v>-0.2986318058569598</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6474</v>
+        <v>6187</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>329.1461750830319</v>
+        <v>347.2191248846516</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>37.45</v>
+        <v>1030</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,49 +4898,49 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.39612967755826</v>
+        <v>45.59198236507806</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.15068740230371</v>
+        <v>12.49047660498223</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4361200887815895</v>
+        <v>1.024155957910955</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3232957930334205</v>
+        <v>-13.13245810298604</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6426</v>
+        <v>6170</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>327.2145612704326</v>
+        <v>342.4213604482667</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>201</v>
+        <v>52.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.33016079521379</v>
+        <v>51.81533579901885</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.1459816705714</v>
+        <v>15.29377246000271</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7819512073020278</v>
+        <v>0.9028279746001536</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.5031530839207718</v>
+        <v>-0.0540520062518024</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6283</v>
+        <v>6188</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>318.9372531969046</v>
+        <v>332.6599658514053</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>24.15</v>
+        <v>80.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.10174320579845</v>
+        <v>50.40393741201001</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.67577201958773</v>
+        <v>15.00704969377108</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.277122608538135</v>
+        <v>1.076589161423931</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0406023699070125</v>
+        <v>0.3392305759736631</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6201</v>
+        <v>6474</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>313.9441410086167</v>
+        <v>329.1461750830319</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>48.65</v>
+        <v>37.45</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.48355469353018</v>
+        <v>51.39612967755826</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.03055137247361</v>
+        <v>13.15068740230371</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.394681963211274</v>
+        <v>0.4361200887815895</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1014248413581653</v>
+        <v>0.3232957930334205</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6183</v>
+        <v>6426</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>309.6959617823784</v>
+        <v>327.2145612704326</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>90.2</v>
+        <v>201</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.8011258595971</v>
+        <v>44.33016079521379</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.52527628920482</v>
+        <v>17.1459816705714</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6437940869040011</v>
+        <v>0.7819512073020278</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.09634373141872141</v>
+        <v>-0.5031530839207718</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6218</v>
+        <v>6283</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>307.3490256773428</v>
+        <v>318.9372531969046</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>36.2</v>
+        <v>24.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.7653791062692</v>
+        <v>52.10174320579845</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.17340257779203</v>
+        <v>13.67577201958773</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2208056360907953</v>
+        <v>0.277122608538135</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0015941185133819</v>
+        <v>-0.0406023699070125</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6203</v>
+        <v>6201</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>302.9062212704424</v>
+        <v>313.9441410086167</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>67.8</v>
+        <v>48.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.25209757665699</v>
+        <v>53.48355469353018</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.75826761550229</v>
+        <v>13.03055137247361</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8293599908132653</v>
+        <v>1.394681963211274</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0331489295064021</v>
+        <v>0.1014248413581653</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6198</v>
+        <v>6183</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>298.0277824515948</v>
+        <v>309.6959617823784</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>20.6</v>
+        <v>90.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.09200530614896</v>
+        <v>49.8011258595971</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6.091883404799644</v>
+        <v>12.52527628920482</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3681139680845189</v>
+        <v>0.6437940869040011</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0722672860963538</v>
+        <v>0.09634373141872141</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6225</v>
+        <v>6218</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>296.6673783063129</v>
+        <v>307.3490256773428</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>23.95</v>
+        <v>36.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.4423715521966</v>
+        <v>47.7653791062692</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.46354692765083</v>
+        <v>13.17340257779203</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2190163892223084</v>
+        <v>0.2208056360907953</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0919122690462629</v>
+        <v>-0.0015941185133819</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6205</v>
+        <v>6203</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>294.6398793101782</v>
+        <v>302.9062212704424</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.25198463917361</v>
+        <v>49.25209757665699</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.4008311489488</v>
+        <v>15.75826761550229</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7223252274279057</v>
+        <v>0.8293599908132653</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.773905791213398</v>
+        <v>0.0331489295064021</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6443</v>
+        <v>6198</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>290.2592686462127</v>
+        <v>298.0277824515948</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>34.45</v>
+        <v>20.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>37.18055700107213</v>
+        <v>51.09200530614896</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.08879443970497</v>
+        <v>6.091883404799644</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2533028669241673</v>
+        <v>0.3681139680845189</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4666406466724011</v>
+        <v>0.0722672860963538</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6184</v>
+        <v>6225</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>289.6652502929248</v>
+        <v>296.6673783063129</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>43.2</v>
+        <v>23.95</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>22.23921190515537</v>
+        <v>54.4423715521966</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>32.86776376076457</v>
+        <v>11.46354692765083</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5728326372683658</v>
+        <v>0.2190163892223084</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3290832393819414</v>
+        <v>0.0919122690462629</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6276</v>
+        <v>6205</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>280.3980865223051</v>
+        <v>294.6398793101782</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>22.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.79765927951438</v>
+        <v>47.25198463917361</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.67369660362069</v>
+        <v>12.4008311489488</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6032649986004743</v>
+        <v>0.7223252274279057</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.041006995970934</v>
+        <v>-0.773905791213398</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6177</v>
+        <v>6443</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>272.4546704076124</v>
+        <v>290.2592686462127</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>45.55</v>
+        <v>34.45</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.7977123562923</v>
+        <v>37.18055700107213</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.32633866376218</v>
+        <v>17.08879443970497</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3012656916859701</v>
+        <v>0.2533028669241673</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1766497704873026</v>
+        <v>-0.4666406466724011</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6442</v>
+        <v>6184</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>271.8809703089873</v>
+        <v>289.6652502929248</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1640</v>
+        <v>43.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.93626488898386</v>
+        <v>22.23921190515537</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.39073810570306</v>
+        <v>32.86776376076457</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9458874754599929</v>
+        <v>0.5728326372683658</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-31.83960365149149</v>
+        <v>-0.3290832393819414</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6277</v>
+        <v>6276</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>269.7413741353101</v>
+        <v>280.3980865223051</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>70.7</v>
+        <v>22.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.19342926828897</v>
+        <v>39.79765927951438</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>28.11879866939151</v>
+        <v>27.67369660362069</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4892291770434804</v>
+        <v>0.6032649986004743</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2751270071446583</v>
+        <v>0.041006995970934</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6165</v>
+        <v>6177</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>265.9163654578311</v>
+        <v>272.4546704076124</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>49.1</v>
+        <v>45.55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>55.44626673083254</v>
+        <v>48.7977123562923</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.19764317168841</v>
+        <v>19.32633866376218</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7970617747460521</v>
+        <v>0.3012656916859701</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0828432372576082</v>
+        <v>-0.1766497704873026</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6206</v>
+        <v>6442</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>265.7395807168485</v>
+        <v>271.8809703089873</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>132.5</v>
+        <v>1640</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>53.15072987276511</v>
+        <v>40.93626488898386</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.11957759556992</v>
+        <v>13.39073810570306</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8983342539736652</v>
+        <v>0.9458874754599929</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.5125594209828161</v>
+        <v>-31.83960365149149</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6405</v>
+        <v>6277</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>263.721461960663</v>
+        <v>269.7413741353101</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>62</v>
+        <v>70.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.4110181704479</v>
+        <v>43.19342926828897</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>19.64677203434592</v>
+        <v>28.11879866939151</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6572709775133075</v>
+        <v>0.4892291770434804</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.312603521270891</v>
+        <v>-0.2751270071446583</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6285</v>
+        <v>6165</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>259.6140639085373</v>
+        <v>265.9163654578311</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>258</v>
+        <v>49.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.28868315523233</v>
+        <v>55.44626673083254</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.93805439925693</v>
+        <v>13.19764317168841</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4389292824009894</v>
+        <v>0.7970617747460521</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.558656053562359</v>
+        <v>0.0828432372576082</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6485</v>
+        <v>6206</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>248.0009142380543</v>
+        <v>265.7395807168485</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>81.3</v>
+        <v>132.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>38.55954715479668</v>
+        <v>53.15072987276511</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.12177236314968</v>
+        <v>14.11957759556992</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.1911558232193111</v>
+        <v>0.8983342539736652</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.9098564303584004</v>
+        <v>-0.5125594209828161</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6222</v>
+        <v>6405</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>236.9451222165128</v>
+        <v>263.721461960663</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>20.55</v>
+        <v>62</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.0049454276319</v>
+        <v>46.4110181704479</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.39012295961778</v>
+        <v>19.64677203434592</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5439630397613591</v>
+        <v>0.6572709775133075</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0243095963918881</v>
+        <v>-1.312603521270891</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6272</v>
+        <v>6285</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>231.9438251940478</v>
+        <v>259.6140639085373</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>32.5</v>
+        <v>258</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.16199866688488</v>
+        <v>47.28868315523233</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.30906872165674</v>
+        <v>18.93805439925693</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6784312032477994</v>
+        <v>0.4389292824009894</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.132858731740288</v>
+        <v>-1.558656053562359</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6216</v>
+        <v>6485</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>230.2304354151901</v>
+        <v>248.0009142380543</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>23.2</v>
+        <v>81.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.29036696604679</v>
+        <v>38.55954715479668</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.1429066127297</v>
+        <v>18.12177236314968</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8417985894603021</v>
+        <v>0.1911558232193111</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0371350929176661</v>
+        <v>-0.9098564303584004</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6416</v>
+        <v>6222</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>214.1549468434485</v>
+        <v>236.9451222165128</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>20.55</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.37991251109442</v>
+        <v>47.0049454276319</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.96785008286004</v>
+        <v>25.39012295961778</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6257884193122272</v>
+        <v>0.5439630397613591</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1118349285128061</v>
+        <v>0.0243095963918881</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6194</v>
+        <v>6272</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>211.286221926316</v>
+        <v>231.9438251940478</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>32.65</v>
+        <v>32.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.27170273367291</v>
+        <v>48.16199866688488</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.40567356859964</v>
+        <v>21.30906872165674</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.869596743390885</v>
+        <v>0.6784312032477994</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0414221962841928</v>
+        <v>-0.132858731740288</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6245</v>
+        <v>6216</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>210.2600798534905</v>
+        <v>230.2304354151901</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>81.8</v>
+        <v>23.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.63829471609661</v>
+        <v>53.29036696604679</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.23006283267671</v>
+        <v>14.1429066127297</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7273011764588538</v>
+        <v>0.8417985894603021</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0782034691530779</v>
+        <v>0.0371350929176661</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6210</v>
+        <v>6416</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>203.4036212567129</v>
+        <v>214.1549468434485</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>19.9</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.77814747697803</v>
+        <v>46.37991251109442</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.66082623517912</v>
+        <v>21.96785008286004</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9825560697757209</v>
+        <v>0.6257884193122272</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0918636923576264</v>
+        <v>-0.1118349285128061</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6441</v>
+        <v>6194</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>191.6108616838291</v>
+        <v>211.286221926316</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>22.55</v>
+        <v>32.65</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.88792429620432</v>
+        <v>50.27170273367291</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.27004885855183</v>
+        <v>11.40567356859964</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7597970331686229</v>
+        <v>0.869596743390885</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0612293046505857</v>
+        <v>0.0414221962841928</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6456</v>
+        <v>6245</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>181.1679834735772</v>
+        <v>210.2600798534905</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.95525830067944</v>
+        <v>49.63829471609661</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.19169490784047</v>
+        <v>15.23006283267671</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7976265068234062</v>
+        <v>0.7273011764588538</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-1.039781458120648</v>
+        <v>-0.0782034691530779</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6236</v>
+        <v>6210</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>164</v>
+        <v>203.4036212567129</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.09235763895681</v>
+        <v>38.77814747697803</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.698617448585641</v>
+        <v>19.66082623517912</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0</v>
+        <v>0.9825560697757209</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,51 +6506,51 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.2400083851950725</v>
+        <v>-0.0918636923576264</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6287</v>
+        <v>6441</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>140.414389535457</v>
+        <v>191.6108616838291</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>22.55</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G115" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>88.86139984269886</v>
+        <v>45.88792429620432</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.15844728477766</v>
+        <v>10.27004885855183</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.7597970331686229</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,221 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0090869411794306</v>
+        <v>0.0612293046505857</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6456</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>GIS-KY</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>181.1679834735772</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>43.95525830067944</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>16.19169490784047</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.7976265068234062</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-1.039781458120648</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>48.09235763895681</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>7.698617448585641</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.2400083851950725</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6287</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>元隆</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>140.414389535457</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>88.86139984269886</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>18.15844728477766</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.3819364013941486</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.0090869411794306</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
         <v>6230</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>尼得科超眾</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
         <v>131.8887187678417</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E119" s="2" t="n">
         <v>127.5</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
         <v>42.85468452458893</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I119" s="2" t="n">
         <v>14.91359760776306</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J119" s="2" t="n">
         <v>0.568851871297505</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
         <v>-0.1711579092822557</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
